--- a/data/trans_bre/IP16B02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 5,91</t>
+          <t>-64,16; 8,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 38,43</t>
+          <t>-31,03; 40,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 50,45</t>
+          <t>-23,65; 51,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,21; 6,22</t>
+          <t>-66,1; 9,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 77,94</t>
+          <t>-34,27; 83,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 124,11</t>
+          <t>-24,97; 124,38</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 25,5</t>
+          <t>-24,89; 23,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -6,66</t>
+          <t>-60,61; -6,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 33,01</t>
+          <t>-25,32; 32,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -6,66</t>
+          <t>-60,61; -6,63</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-64,59; 27,14</t>
+          <t>-64,35; 25,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 17,49</t>
+          <t>-31,95; 19,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 0,0</t>
+          <t>-57,4; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-78,85; 54,24</t>
+          <t>-83,67; 36,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 22,42</t>
+          <t>-33,31; 24,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 0,0</t>
+          <t>-57,4; 0,0</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 19,95</t>
+          <t>-25,88; 20,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 18,46</t>
+          <t>-13,04; 19,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 31,76</t>
+          <t>-6,04; 32,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 26,6</t>
+          <t>-28,03; 29,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 24,64</t>
+          <t>-13,97; 27,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 47,01</t>
+          <t>-6,15; 49,97</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 14,79</t>
+          <t>-33,89; 14,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -7,07</t>
+          <t>-45,19; -7,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-53,66; -13,43</t>
+          <t>-56,06; -14,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 17,33</t>
+          <t>-34,11; 17,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,89; -8,03</t>
+          <t>-48,04; -9,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,66; -13,43</t>
+          <t>-56,06; -14,38</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 0,0</t>
+          <t>-53,91; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,28</t>
+          <t>0,0; 61,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 0,0</t>
+          <t>-53,91; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 256,7</t>
+          <t>0,0; 158,61</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 4,3</t>
+          <t>-18,81; 5,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 2,45</t>
+          <t>-15,81; 3,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 2,97</t>
+          <t>-17,26; 3,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 4,8</t>
+          <t>-20,52; 5,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 2,93</t>
+          <t>-17,02; 3,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 3,49</t>
+          <t>-18,71; 3,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 8,47</t>
+          <t>-62,58; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 40,86</t>
+          <t>-32,69; 41,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 51,2</t>
+          <t>-26,73; 49,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 9,7</t>
+          <t>-65,2; 6,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 83,38</t>
+          <t>-36,47; 84,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 124,38</t>
+          <t>-27,73; 115,37</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 23,83</t>
+          <t>-24,56; 22,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -6,63</t>
+          <t>-64,43; -6,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 32,92</t>
+          <t>-25,4; 31,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -6,63</t>
+          <t>-64,43; -6,73</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-64,35; 25,22</t>
+          <t>-65,18; 27,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 19,61</t>
+          <t>-30,37; 19,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 0,0</t>
+          <t>-59,17; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-83,67; 36,61</t>
+          <t>-82,72; 44,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 24,58</t>
+          <t>-32,85; 23,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 0,0</t>
+          <t>-59,17; 0,0</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 20,59</t>
+          <t>-27,25; 18,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 19,79</t>
+          <t>-12,76; 19,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 32,51</t>
+          <t>-5,8; 29,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 29,03</t>
+          <t>-31,49; 23,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 27,01</t>
+          <t>-13,76; 26,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 49,97</t>
+          <t>-5,79; 46,03</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 14,87</t>
+          <t>-34,83; 14,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -7,12</t>
+          <t>-46,83; -6,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -14,38</t>
+          <t>-55,89; -15,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 17,34</t>
+          <t>-38,45; 17,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,04; -9,3</t>
+          <t>-48,98; -7,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -14,38</t>
+          <t>-55,89; -15,28</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 0,0</t>
+          <t>-50,29; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,37</t>
+          <t>0,0; 67,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 0,0</t>
+          <t>-50,29; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 158,61</t>
+          <t>0,0; 204,61</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 5,34</t>
+          <t>-18,34; 5,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 3,23</t>
+          <t>-16,48; 2,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 3,02</t>
+          <t>-17,04; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 5,94</t>
+          <t>-19,52; 6,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 3,87</t>
+          <t>-18,27; 2,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 3,43</t>
+          <t>-18,3; 3,63</t>
         </is>
       </c>
     </row>
